--- a/output/graficos_nacionales/plot_nacional_o_ocup_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_o_ocup_a_2020.xlsx
@@ -15543,7 +15543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de ocupación formal dependiente</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_o_ocup_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_o_ocup_a_2020.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="704">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
     <t xml:space="preserve">12302</t>
@@ -328,6 +328,21 @@
     <t xml:space="preserve">Maipú</t>
   </si>
   <si>
+    <t xml:space="preserve">Valparaiso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
     <t xml:space="preserve">6101</t>
   </si>
   <si>
@@ -400,18 +415,18 @@
     <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
+    <t xml:space="preserve">13110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
     <t xml:space="preserve">7306</t>
   </si>
   <si>
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
-    <t xml:space="preserve">13110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
     <t xml:space="preserve">13127</t>
   </si>
   <si>
@@ -472,6 +487,12 @@
     <t xml:space="preserve">Doñihue</t>
   </si>
   <si>
+    <t xml:space="preserve">5102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
     <t xml:space="preserve">6107</t>
   </si>
   <si>
@@ -484,6 +505,12 @@
     <t xml:space="preserve">Talagante</t>
   </si>
   <si>
+    <t xml:space="preserve">5606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
     <t xml:space="preserve">6303</t>
   </si>
   <si>
@@ -496,12 +523,36 @@
     <t xml:space="preserve">Palmilla</t>
   </si>
   <si>
+    <t xml:space="preserve">5301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
+  </si>
+  <si>
     <t xml:space="preserve">6110</t>
   </si>
   <si>
     <t xml:space="preserve">Mostazal</t>
   </si>
   <si>
+    <t xml:space="preserve">5302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
     <t xml:space="preserve">7101</t>
   </si>
   <si>
@@ -520,6 +571,12 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">5304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
     <t xml:space="preserve">13603</t>
   </si>
   <si>
@@ -532,6 +589,18 @@
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
+    <t xml:space="preserve">5503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
     <t xml:space="preserve">13129</t>
   </si>
   <si>
@@ -568,6 +637,18 @@
     <t xml:space="preserve">San José de Maipo</t>
   </si>
   <si>
+    <t xml:space="preserve">5501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
     <t xml:space="preserve">7110</t>
   </si>
   <si>
@@ -628,12 +709,36 @@
     <t xml:space="preserve">7105</t>
   </si>
   <si>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
+  </si>
+  <si>
     <t xml:space="preserve">7102</t>
   </si>
   <si>
     <t xml:space="preserve">Constitución</t>
   </si>
   <si>
+    <t xml:space="preserve">5109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
     <t xml:space="preserve">13504</t>
   </si>
   <si>
@@ -646,18 +751,48 @@
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
+    <t xml:space="preserve">5802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limache</t>
+  </si>
+  <si>
     <t xml:space="preserve">13116</t>
   </si>
   <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
+    <t xml:space="preserve">5402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
     <t xml:space="preserve">13111</t>
   </si>
   <si>
     <t xml:space="preserve">La Granja</t>
   </si>
   <si>
+    <t xml:space="preserve">5601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
     <t xml:space="preserve">7406</t>
   </si>
   <si>
@@ -670,6 +805,12 @@
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
+    <t xml:space="preserve">5804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
     <t xml:space="preserve">6109</t>
   </si>
   <si>
@@ -688,6 +829,12 @@
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
+    <t xml:space="preserve">5101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">13112</t>
   </si>
   <si>
@@ -706,6 +853,12 @@
     <t xml:space="preserve">San Ramón</t>
   </si>
   <si>
+    <t xml:space="preserve">5405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
     <t xml:space="preserve">6114</t>
   </si>
   <si>
@@ -718,6 +871,12 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">5404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
     <t xml:space="preserve">7408</t>
   </si>
   <si>
@@ -742,6 +901,12 @@
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">16102</t>
   </si>
   <si>
@@ -766,6 +931,18 @@
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
+    <t xml:space="preserve">5107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
     <t xml:space="preserve">6103</t>
   </si>
   <si>
@@ -790,6 +967,12 @@
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
+    <t xml:space="preserve">5705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
     <t xml:space="preserve">16201</t>
   </si>
   <si>
@@ -832,12 +1015,24 @@
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
+    <t xml:space="preserve">5105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
     <t xml:space="preserve">6202</t>
   </si>
   <si>
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
+    <t xml:space="preserve">5803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
     <t xml:space="preserve">16105</t>
   </si>
   <si>
@@ -880,6 +1075,12 @@
     <t xml:space="preserve">Curepto</t>
   </si>
   <si>
+    <t xml:space="preserve">5602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
     <t xml:space="preserve">16205</t>
   </si>
   <si>
@@ -916,6 +1117,18 @@
     <t xml:space="preserve">Paredones</t>
   </si>
   <si>
+    <t xml:space="preserve">5603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
     <t xml:space="preserve">16304</t>
   </si>
   <si>
@@ -958,6 +1171,12 @@
     <t xml:space="preserve">Navidad</t>
   </si>
   <si>
+    <t xml:space="preserve">5605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
     <t xml:space="preserve">7203</t>
   </si>
   <si>
@@ -970,6 +1189,138 @@
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">norte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrozona Norte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copiapó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapaca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iquique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra Amarilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicuña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozo Almonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Serena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ovalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallenar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Hospicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocopilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monte Patria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arica y Parinacota</t>
   </si>
   <si>
@@ -979,10 +1330,94 @@
     <t xml:space="preserve">Arica</t>
   </si>
   <si>
-    <t xml:space="preserve">norte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macrozona Norte</t>
+    <t xml:space="preserve">4201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro de Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andacollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punitaqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combarbalá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto del Carmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Vilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Higuera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiña</t>
   </si>
   <si>
     <t xml:space="preserve">Los Lagos</t>
@@ -1159,18 +1594,18 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
+    <t xml:space="preserve">8305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
     <t xml:space="preserve">9209</t>
   </si>
   <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
-    <t xml:space="preserve">8305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
     <t xml:space="preserve">10102</t>
   </si>
   <si>
@@ -1648,7 +2083,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:26</t>
+    <t xml:space="preserve">2026-09-07 13:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1660,16 +2095,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_o_ocup_a_2020.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Tasa de ocupacion formal dependiente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -3442,16 +3886,16 @@
         <v>2020</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>48</v>
@@ -3463,7 +3907,7 @@
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>40.96</v>
+        <v>41.12</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3474,16 +3918,16 @@
         <v>2020</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>48</v>
@@ -3495,7 +3939,7 @@
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>40.95</v>
+        <v>41.03</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3512,10 +3956,10 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>48</v>
@@ -3527,7 +3971,7 @@
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>40.92</v>
+        <v>40.96</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -3538,16 +3982,16 @@
         <v>2020</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>48</v>
@@ -3559,7 +4003,7 @@
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>40.74</v>
+        <v>40.95</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -3576,10 +4020,10 @@
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>48</v>
@@ -3591,7 +4035,7 @@
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>40.45</v>
+        <v>40.92</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -3608,10 +4052,10 @@
         <v>86</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>48</v>
@@ -3623,7 +4067,7 @@
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>40.41</v>
+        <v>40.74</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -3634,16 +4078,16 @@
         <v>2020</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>48</v>
@@ -3655,7 +4099,7 @@
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>40.4</v>
+        <v>40.45</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -3672,10 +4116,10 @@
         <v>86</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>48</v>
@@ -3687,7 +4131,7 @@
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>40.34</v>
+        <v>40.41</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -3698,16 +4142,16 @@
         <v>2020</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>48</v>
@@ -3719,7 +4163,7 @@
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>40.1</v>
+        <v>40.4</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -3730,16 +4174,16 @@
         <v>2020</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>48</v>
@@ -3751,7 +4195,7 @@
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>40.02</v>
+        <v>40.34</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -3762,16 +4206,16 @@
         <v>2020</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>48</v>
@@ -3783,7 +4227,7 @@
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>39.96</v>
+        <v>40.1</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -3800,10 +4244,10 @@
         <v>45</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>48</v>
@@ -3815,7 +4259,7 @@
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>39.86</v>
+        <v>40.02</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -3826,16 +4270,16 @@
         <v>2020</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>48</v>
@@ -3847,7 +4291,7 @@
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>39.84</v>
+        <v>39.96</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -3864,10 +4308,10 @@
         <v>45</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>48</v>
@@ -3879,7 +4323,7 @@
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>39.84</v>
+        <v>39.86</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -3896,10 +4340,10 @@
         <v>45</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>48</v>
@@ -3911,7 +4355,7 @@
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>39.52</v>
+        <v>39.84</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -3922,16 +4366,16 @@
         <v>2020</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>48</v>
@@ -3943,7 +4387,7 @@
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>39.51</v>
+        <v>39.84</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -3954,16 +4398,16 @@
         <v>2020</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>48</v>
@@ -3975,7 +4419,7 @@
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>39.45</v>
+        <v>39.52</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -3992,10 +4436,10 @@
         <v>45</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>48</v>
@@ -4007,7 +4451,7 @@
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>39.39</v>
+        <v>39.51</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4018,16 +4462,16 @@
         <v>2020</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>48</v>
@@ -4039,7 +4483,7 @@
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39.38</v>
+        <v>39.45</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4056,10 +4500,10 @@
         <v>45</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>48</v>
@@ -4071,7 +4515,7 @@
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>39.36</v>
+        <v>39.39</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4088,10 +4532,10 @@
         <v>45</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>48</v>
@@ -4103,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>39.35</v>
+        <v>39.38</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4120,10 +4564,10 @@
         <v>45</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>48</v>
@@ -4135,7 +4579,7 @@
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>39.2</v>
+        <v>39.36</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4146,16 +4590,16 @@
         <v>2020</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>48</v>
@@ -4167,7 +4611,7 @@
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>39.08</v>
+        <v>39.35</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4178,16 +4622,16 @@
         <v>2020</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>48</v>
@@ -4199,7 +4643,7 @@
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4216,10 +4660,10 @@
         <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>48</v>
@@ -4231,7 +4675,7 @@
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>38.88</v>
+        <v>39.08</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4242,16 +4686,16 @@
         <v>2020</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>48</v>
@@ -4263,7 +4707,7 @@
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>38.72</v>
+        <v>39</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4274,16 +4718,16 @@
         <v>2020</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>48</v>
@@ -4295,7 +4739,7 @@
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>38.56</v>
+        <v>38.92</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4312,10 +4756,10 @@
         <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>48</v>
@@ -4327,7 +4771,7 @@
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>38.54</v>
+        <v>38.88</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4338,16 +4782,16 @@
         <v>2020</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>48</v>
@@ -4359,7 +4803,7 @@
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38.26</v>
+        <v>38.72</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4370,16 +4814,16 @@
         <v>2020</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>48</v>
@@ -4391,7 +4835,7 @@
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>38.02</v>
+        <v>38.67</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4402,16 +4846,16 @@
         <v>2020</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>48</v>
@@ -4423,7 +4867,7 @@
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>37.94</v>
+        <v>38.56</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4434,16 +4878,16 @@
         <v>2020</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>48</v>
@@ -4455,7 +4899,7 @@
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>37.86</v>
+        <v>38.54</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4466,16 +4910,16 @@
         <v>2020</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>48</v>
@@ -4487,7 +4931,7 @@
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>37.76</v>
+        <v>38.47</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4498,16 +4942,16 @@
         <v>2020</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>48</v>
@@ -4519,7 +4963,7 @@
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>37.62</v>
+        <v>38.47</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -4530,16 +4974,16 @@
         <v>2020</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>48</v>
@@ -4551,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>37.15</v>
+        <v>38.26</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -4562,16 +5006,16 @@
         <v>2020</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>48</v>
@@ -4583,7 +5027,7 @@
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>37.1</v>
+        <v>38.25</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -4594,16 +5038,16 @@
         <v>2020</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>48</v>
@@ -4615,7 +5059,7 @@
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>36.88</v>
+        <v>38.2</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -4626,16 +5070,16 @@
         <v>2020</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>48</v>
@@ -4647,7 +5091,7 @@
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>36.85</v>
+        <v>38.02</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -4658,16 +5102,16 @@
         <v>2020</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>48</v>
@@ -4679,7 +5123,7 @@
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>36.79</v>
+        <v>37.94</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -4696,10 +5140,10 @@
         <v>45</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>48</v>
@@ -4711,7 +5155,7 @@
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>36.76</v>
+        <v>37.86</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -4722,16 +5166,16 @@
         <v>2020</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>48</v>
@@ -4743,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>36.62</v>
+        <v>37.79</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -4754,10 +5198,10 @@
         <v>2020</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>186</v>
@@ -4775,7 +5219,7 @@
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>36.62</v>
+        <v>37.76</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -4786,10 +5230,10 @@
         <v>2020</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>188</v>
@@ -4807,7 +5251,7 @@
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>36.57</v>
+        <v>37.62</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -4818,10 +5262,10 @@
         <v>2020</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>190</v>
@@ -4839,7 +5283,7 @@
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>36.56</v>
+        <v>37.59</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -4850,10 +5294,10 @@
         <v>2020</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>192</v>
@@ -4871,7 +5315,7 @@
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>36.52</v>
+        <v>37.51</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -4903,7 +5347,7 @@
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>36.49</v>
+        <v>37.15</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -4935,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>36.46</v>
+        <v>37.1</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -4946,10 +5390,10 @@
         <v>2020</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>198</v>
@@ -4967,7 +5411,7 @@
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>36.23</v>
+        <v>36.88</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -4978,10 +5422,10 @@
         <v>2020</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>200</v>
@@ -4999,7 +5443,7 @@
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>36.21</v>
+        <v>36.85</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5010,16 +5454,16 @@
         <v>2020</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>202</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>48</v>
@@ -5031,7 +5475,7 @@
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>36.18</v>
+        <v>36.79</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5042,16 +5486,16 @@
         <v>2020</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>48</v>
@@ -5063,7 +5507,7 @@
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>36.01</v>
+        <v>36.76</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5074,16 +5518,16 @@
         <v>2020</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>48</v>
@@ -5095,7 +5539,7 @@
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>35.9</v>
+        <v>36.74</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5106,16 +5550,16 @@
         <v>2020</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>48</v>
@@ -5127,7 +5571,7 @@
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>35.81</v>
+        <v>36.71</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5138,16 +5582,16 @@
         <v>2020</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>48</v>
@@ -5159,7 +5603,7 @@
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>35.76</v>
+        <v>36.62</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5170,16 +5614,16 @@
         <v>2020</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>45</v>
+        <v>212</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>48</v>
@@ -5191,7 +5635,7 @@
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>35.39</v>
+        <v>36.62</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5208,10 +5652,10 @@
         <v>86</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>48</v>
@@ -5223,7 +5667,7 @@
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>35.24</v>
+        <v>36.57</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5234,16 +5678,16 @@
         <v>2020</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>48</v>
@@ -5255,7 +5699,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>35.17</v>
+        <v>36.56</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5266,16 +5710,16 @@
         <v>2020</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>48</v>
@@ -5287,7 +5731,7 @@
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>34.89</v>
+        <v>36.52</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5304,10 +5748,10 @@
         <v>45</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>48</v>
@@ -5319,7 +5763,7 @@
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>34.81</v>
+        <v>36.49</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5330,16 +5774,16 @@
         <v>2020</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>48</v>
@@ -5351,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>34.77</v>
+        <v>36.46</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5368,10 +5812,10 @@
         <v>45</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>48</v>
@@ -5383,7 +5827,7 @@
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>34.44</v>
+        <v>36.23</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5394,16 +5838,16 @@
         <v>2020</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>48</v>
@@ -5415,7 +5859,7 @@
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>34.36</v>
+        <v>36.21</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5426,16 +5870,16 @@
         <v>2020</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>48</v>
@@ -5447,7 +5891,7 @@
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>34.33</v>
+        <v>36.18</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5458,16 +5902,16 @@
         <v>2020</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>48</v>
@@ -5479,7 +5923,7 @@
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>33.84</v>
+        <v>36.14</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5490,16 +5934,16 @@
         <v>2020</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>48</v>
@@ -5511,7 +5955,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>33.7</v>
+        <v>36.05</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -5528,10 +5972,10 @@
         <v>86</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>48</v>
@@ -5543,7 +5987,7 @@
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>33.53</v>
+        <v>36.01</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -5554,16 +5998,16 @@
         <v>2020</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>48</v>
@@ -5575,7 +6019,7 @@
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>33.36</v>
+        <v>35.99</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -5586,16 +6030,16 @@
         <v>2020</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>48</v>
@@ -5607,7 +6051,7 @@
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>33.35</v>
+        <v>35.96</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -5618,16 +6062,16 @@
         <v>2020</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>48</v>
@@ -5639,7 +6083,7 @@
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>33.19</v>
+        <v>35.9</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -5653,13 +6097,13 @@
         <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>48</v>
@@ -5671,7 +6115,7 @@
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>32.99</v>
+        <v>35.81</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -5682,16 +6126,16 @@
         <v>2020</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>48</v>
@@ -5703,7 +6147,7 @@
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>32.98</v>
+        <v>35.76</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -5714,16 +6158,16 @@
         <v>2020</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>48</v>
@@ -5735,7 +6179,7 @@
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>32.39</v>
+        <v>35.76</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -5746,16 +6190,16 @@
         <v>2020</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>48</v>
@@ -5767,7 +6211,7 @@
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>32.22</v>
+        <v>35.7</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -5778,16 +6222,16 @@
         <v>2020</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>48</v>
@@ -5799,7 +6243,7 @@
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>31.75</v>
+        <v>35.68</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -5810,16 +6254,16 @@
         <v>2020</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>48</v>
@@ -5831,7 +6275,7 @@
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>31.61</v>
+        <v>35.39</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -5842,16 +6286,16 @@
         <v>2020</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>48</v>
@@ -5863,7 +6307,7 @@
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>31.41</v>
+        <v>35.38</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -5874,16 +6318,16 @@
         <v>2020</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>48</v>
@@ -5895,7 +6339,7 @@
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>31.28</v>
+        <v>35.24</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -5906,16 +6350,16 @@
         <v>2020</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>48</v>
@@ -5927,7 +6371,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>31.04</v>
+        <v>35.24</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -5938,16 +6382,16 @@
         <v>2020</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>48</v>
@@ -5959,7 +6403,7 @@
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>30.96</v>
+        <v>35.17</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -5970,16 +6414,16 @@
         <v>2020</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>48</v>
@@ -5991,7 +6435,7 @@
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>30.7</v>
+        <v>35.1</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6002,16 +6446,16 @@
         <v>2020</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>48</v>
@@ -6023,7 +6467,7 @@
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>30.67</v>
+        <v>34.89</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6034,16 +6478,16 @@
         <v>2020</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>48</v>
@@ -6055,7 +6499,7 @@
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>30.63</v>
+        <v>34.81</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6066,16 +6510,16 @@
         <v>2020</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>48</v>
@@ -6087,7 +6531,7 @@
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>30.47</v>
+        <v>34.77</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6098,16 +6542,16 @@
         <v>2020</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>48</v>
@@ -6119,7 +6563,7 @@
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>30.01</v>
+        <v>34.55</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6130,16 +6574,16 @@
         <v>2020</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>48</v>
@@ -6151,7 +6595,7 @@
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>29.94</v>
+        <v>34.44</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6162,16 +6606,16 @@
         <v>2020</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>48</v>
@@ -6183,7 +6627,7 @@
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>29.7</v>
+        <v>34.36</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6194,16 +6638,16 @@
         <v>2020</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>48</v>
@@ -6215,7 +6659,7 @@
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>29.65</v>
+        <v>34.33</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6226,16 +6670,16 @@
         <v>2020</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>48</v>
@@ -6247,7 +6691,7 @@
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>29.46</v>
+        <v>34.21</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6264,10 +6708,10 @@
         <v>28</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>48</v>
@@ -6279,7 +6723,7 @@
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>29.42</v>
+        <v>33.84</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6296,10 +6740,10 @@
         <v>86</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>48</v>
@@ -6311,7 +6755,7 @@
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>28.92</v>
+        <v>33.7</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>15</v>
@@ -6322,16 +6766,16 @@
         <v>2020</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>48</v>
@@ -6343,7 +6787,7 @@
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>28.63</v>
+        <v>33.64</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6360,10 +6804,10 @@
         <v>86</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>48</v>
@@ -6375,7 +6819,7 @@
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>27.36</v>
+        <v>33.53</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6386,16 +6830,16 @@
         <v>2020</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>48</v>
@@ -6407,7 +6851,7 @@
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>26.94</v>
+        <v>33.36</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6418,16 +6862,16 @@
         <v>2020</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>48</v>
@@ -6439,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>26.92</v>
+        <v>33.35</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6450,16 +6894,16 @@
         <v>2020</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>48</v>
@@ -6471,7 +6915,7 @@
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>26.84</v>
+        <v>33.19</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6482,16 +6926,16 @@
         <v>2020</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>48</v>
@@ -6503,7 +6947,7 @@
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>26.77</v>
+        <v>33.16</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -6517,13 +6961,13 @@
         <v>16</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>48</v>
@@ -6535,7 +6979,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>26.75</v>
+        <v>32.99</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>15</v>
@@ -6552,10 +6996,10 @@
         <v>28</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>48</v>
@@ -6567,7 +7011,7 @@
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>26.58</v>
+        <v>32.98</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -6581,13 +7025,13 @@
         <v>16</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>48</v>
@@ -6599,7 +7043,7 @@
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>24.78</v>
+        <v>32.39</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>15</v>
@@ -6616,10 +7060,10 @@
         <v>86</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>48</v>
@@ -6631,7 +7075,7 @@
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>24.59</v>
+        <v>32.22</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -6642,16 +7086,16 @@
         <v>2020</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>48</v>
@@ -6663,7 +7107,7 @@
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>24.49</v>
+        <v>31.84</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -6674,16 +7118,16 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>48</v>
@@ -6695,7 +7139,7 @@
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>24.43</v>
+        <v>31.83</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>15</v>
@@ -6706,16 +7150,16 @@
         <v>2020</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>185</v>
+        <v>28</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>48</v>
@@ -6727,7 +7171,7 @@
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>24.37</v>
+        <v>31.75</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -6741,13 +7185,13 @@
         <v>16</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>48</v>
@@ -6759,7 +7203,7 @@
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>24.35</v>
+        <v>31.61</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -6770,16 +7214,16 @@
         <v>2020</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>48</v>
@@ -6791,7 +7235,7 @@
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>23.5</v>
+        <v>31.41</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -6802,16 +7246,16 @@
         <v>2020</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>48</v>
@@ -6823,7 +7267,7 @@
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>22.11</v>
+        <v>31.28</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -6834,16 +7278,16 @@
         <v>2020</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>48</v>
@@ -6855,7 +7299,7 @@
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>21.58</v>
+        <v>31.04</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -6866,10 +7310,10 @@
         <v>2020</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>317</v>
+        <v>212</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>318</v>
@@ -6878,16 +7322,16 @@
         <v>319</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>320</v>
+        <v>48</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>321</v>
+        <v>49</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>34.4</v>
+        <v>31.04</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -6898,28 +7342,28 @@
         <v>2020</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>43.56</v>
+        <v>30.96</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -6930,28 +7374,28 @@
         <v>2020</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="E153" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>41.42</v>
+        <v>30.7</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -6962,28 +7406,28 @@
         <v>2020</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>322</v>
+        <v>86</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>41.29</v>
+        <v>30.67</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -6994,28 +7438,28 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>40.51</v>
+        <v>30.63</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7026,28 +7470,28 @@
         <v>2020</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>40.46</v>
+        <v>30.47</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7058,28 +7502,28 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="F157" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>39.86</v>
+        <v>30.01</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>15</v>
@@ -7090,28 +7534,28 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>322</v>
+        <v>103</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>39.63</v>
+        <v>29.99</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7122,28 +7566,28 @@
         <v>2020</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>39.45</v>
+        <v>29.94</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7154,28 +7598,28 @@
         <v>2020</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>39.21</v>
+        <v>29.92</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7186,28 +7630,28 @@
         <v>2020</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>38.95</v>
+        <v>29.7</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7218,28 +7662,28 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>38.55</v>
+        <v>29.65</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7250,28 +7694,28 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>38.33</v>
+        <v>29.46</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7282,28 +7726,28 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>350</v>
+        <v>28</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>38.33</v>
+        <v>29.42</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7314,28 +7758,28 @@
         <v>2020</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>322</v>
+        <v>86</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>38.3</v>
+        <v>28.92</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7346,28 +7790,28 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>38.25</v>
+        <v>28.63</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7378,28 +7822,28 @@
         <v>2020</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>357</v>
+        <v>86</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>38.09</v>
+        <v>27.36</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7410,28 +7854,28 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>37.15</v>
+        <v>26.94</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7442,28 +7886,28 @@
         <v>2020</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>36.86</v>
+        <v>26.94</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7474,28 +7918,28 @@
         <v>2020</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>36.74</v>
+        <v>26.92</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -7506,28 +7950,28 @@
         <v>2020</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>350</v>
+        <v>212</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>36.64</v>
+        <v>26.84</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -7538,28 +7982,28 @@
         <v>2020</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>36.64</v>
+        <v>26.77</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -7570,28 +8014,28 @@
         <v>2020</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>36.62</v>
+        <v>26.75</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -7602,28 +8046,28 @@
         <v>2020</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>36.52</v>
+        <v>26.58</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -7634,28 +8078,28 @@
         <v>2020</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>322</v>
+        <v>103</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>36.04</v>
+        <v>25.33</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -7666,28 +8110,28 @@
         <v>2020</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>35.71</v>
+        <v>25.12</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -7698,28 +8142,28 @@
         <v>2020</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>34.8</v>
+        <v>24.78</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -7730,28 +8174,28 @@
         <v>2020</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>350</v>
+        <v>86</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>34.72</v>
+        <v>24.59</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -7762,28 +8206,28 @@
         <v>2020</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>34.72</v>
+        <v>24.49</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -7794,28 +8238,28 @@
         <v>2020</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>34.66</v>
+        <v>24.43</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -7826,28 +8270,28 @@
         <v>2020</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>357</v>
+        <v>212</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>322</v>
+        <v>379</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>34.6</v>
+        <v>24.37</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -7858,28 +8302,28 @@
         <v>2020</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>34.58</v>
+        <v>24.35</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -7890,28 +8334,28 @@
         <v>2020</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>34.45</v>
+        <v>23.5</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -7922,28 +8366,28 @@
         <v>2020</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>350</v>
+        <v>103</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>34.34</v>
+        <v>22.3</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -7954,28 +8398,28 @@
         <v>2020</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>322</v>
+        <v>86</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>34.26</v>
+        <v>22.11</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -7986,28 +8430,28 @@
         <v>2020</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>325</v>
+        <v>48</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>326</v>
+        <v>49</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>34.02</v>
+        <v>21.58</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8018,28 +8462,28 @@
         <v>2020</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>34.02</v>
+        <v>45.43</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8050,28 +8494,28 @@
         <v>2020</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>34.02</v>
+        <v>44.2</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8082,28 +8526,28 @@
         <v>2020</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>33.92</v>
+        <v>43.75</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8114,28 +8558,28 @@
         <v>2020</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>33.65</v>
+        <v>43.21</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8146,28 +8590,28 @@
         <v>2020</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>33.56</v>
+        <v>42.58</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8178,28 +8622,28 @@
         <v>2020</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>33.51</v>
+        <v>39.35</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8210,28 +8654,28 @@
         <v>2020</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>33.51</v>
+        <v>37.53</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8242,28 +8686,28 @@
         <v>2020</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>331</v>
+        <v>398</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>33.37</v>
+        <v>37.17</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8274,28 +8718,28 @@
         <v>2020</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>33.24</v>
+        <v>36.69</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8306,28 +8750,28 @@
         <v>2020</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>32.99</v>
+        <v>36.67</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8338,28 +8782,28 @@
         <v>2020</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>32.9</v>
+        <v>36.35</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8370,28 +8814,28 @@
         <v>2020</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>32.89</v>
+        <v>36.12</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8402,28 +8846,28 @@
         <v>2020</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>32.88</v>
+        <v>36.07</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8434,28 +8878,28 @@
         <v>2020</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>32.85</v>
+        <v>36.01</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8466,28 +8910,28 @@
         <v>2020</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>32.79</v>
+        <v>35.87</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>15</v>
@@ -8498,28 +8942,28 @@
         <v>2020</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>32.45</v>
+        <v>35.58</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8530,28 +8974,28 @@
         <v>2020</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>32.39</v>
+        <v>35.57</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -8562,28 +9006,28 @@
         <v>2020</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>32.35</v>
+        <v>35.51</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -8594,28 +9038,28 @@
         <v>2020</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>31.74</v>
+        <v>35.39</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -8626,28 +9070,28 @@
         <v>2020</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>31.68</v>
+        <v>35.3</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -8658,28 +9102,28 @@
         <v>2020</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>322</v>
+        <v>434</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>31.59</v>
+        <v>34.4</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -8690,28 +9134,28 @@
         <v>2020</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>31.48</v>
+        <v>33.99</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -8722,28 +9166,28 @@
         <v>2020</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>31.47</v>
+        <v>33.52</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>15</v>
@@ -8754,28 +9198,28 @@
         <v>2020</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>31.46</v>
+        <v>32.9</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>15</v>
@@ -8786,28 +9230,28 @@
         <v>2020</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>31.4</v>
+        <v>32.82</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>15</v>
@@ -8818,28 +9262,28 @@
         <v>2020</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>30.64</v>
+        <v>32.2</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>15</v>
@@ -8850,28 +9294,28 @@
         <v>2020</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>30.63</v>
+        <v>32.1</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>15</v>
@@ -8882,28 +9326,28 @@
         <v>2020</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>322</v>
+        <v>403</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>30.62</v>
+        <v>31.22</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>15</v>
@@ -8914,28 +9358,28 @@
         <v>2020</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>30.25</v>
+        <v>30.34</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>15</v>
@@ -8946,28 +9390,28 @@
         <v>2020</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>30.15</v>
+        <v>27.78</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>15</v>
@@ -8978,28 +9422,28 @@
         <v>2020</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>15</v>
@@ -9010,28 +9454,28 @@
         <v>2020</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>29.94</v>
+        <v>27.48</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>15</v>
@@ -9042,28 +9486,28 @@
         <v>2020</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>29.91</v>
+        <v>26.05</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>15</v>
@@ -9074,28 +9518,28 @@
         <v>2020</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>29.35</v>
+        <v>24.27</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>15</v>
@@ -9106,28 +9550,28 @@
         <v>2020</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>29.34</v>
+        <v>23.77</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>15</v>
@@ -9138,28 +9582,28 @@
         <v>2020</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>322</v>
+        <v>403</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>29.29</v>
+        <v>16.73</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>15</v>
@@ -9170,28 +9614,28 @@
         <v>2020</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>357</v>
+        <v>467</v>
       </c>
       <c r="D223" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="E223" s="2" t="s">
+      <c r="F223" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="F223" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="G223" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>29.1</v>
+        <v>43.56</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>15</v>
@@ -9202,28 +9646,28 @@
         <v>2020</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D224" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G224" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="E224" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>29.02</v>
+        <v>41.42</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>15</v>
@@ -9234,28 +9678,28 @@
         <v>2020</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>28.88</v>
+        <v>41.29</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>15</v>
@@ -9269,25 +9713,25 @@
         <v>8</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>28.68</v>
+        <v>40.51</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>15</v>
@@ -9298,28 +9742,28 @@
         <v>2020</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>322</v>
+        <v>476</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>28.31</v>
+        <v>40.46</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>15</v>
@@ -9330,28 +9774,28 @@
         <v>2020</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>322</v>
+        <v>476</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>28.1</v>
+        <v>39.86</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>15</v>
@@ -9362,28 +9806,28 @@
         <v>2020</v>
       </c>
       <c r="B229" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>331</v>
+        <v>467</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>28</v>
+        <v>39.63</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>15</v>
@@ -9397,25 +9841,25 @@
         <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>27.81</v>
+        <v>39.45</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>15</v>
@@ -9426,28 +9870,28 @@
         <v>2020</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>27.69</v>
+        <v>39.21</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>15</v>
@@ -9458,28 +9902,28 @@
         <v>2020</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>27.58</v>
+        <v>38.95</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>15</v>
@@ -9490,28 +9934,28 @@
         <v>2020</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>357</v>
+        <v>476</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>27.38</v>
+        <v>38.55</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>15</v>
@@ -9525,25 +9969,25 @@
         <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>27.21</v>
+        <v>38.33</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>15</v>
@@ -9554,28 +9998,28 @@
         <v>2020</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>322</v>
+        <v>495</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>27.15</v>
+        <v>38.33</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>15</v>
@@ -9586,28 +10030,28 @@
         <v>2020</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>331</v>
+        <v>467</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>27.11</v>
+        <v>38.3</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>15</v>
@@ -9621,25 +10065,25 @@
         <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>26.93</v>
+        <v>38.25</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>15</v>
@@ -9650,28 +10094,28 @@
         <v>2020</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>350</v>
+        <v>502</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>26.91</v>
+        <v>38.09</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>15</v>
@@ -9685,25 +10129,25 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>26.82</v>
+        <v>37.15</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>15</v>
@@ -9714,28 +10158,28 @@
         <v>2020</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>322</v>
+        <v>476</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>25.81</v>
+        <v>36.86</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>15</v>
@@ -9746,28 +10190,28 @@
         <v>2020</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>25.5</v>
+        <v>36.74</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>15</v>
@@ -9778,28 +10222,28 @@
         <v>2020</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>331</v>
+        <v>495</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>25.46</v>
+        <v>36.64</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>15</v>
@@ -9810,28 +10254,28 @@
         <v>2020</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>25.36</v>
+        <v>36.64</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>15</v>
@@ -9842,28 +10286,28 @@
         <v>2020</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>25.22</v>
+        <v>36.62</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>15</v>
@@ -9874,28 +10318,28 @@
         <v>2020</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>357</v>
+        <v>476</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>24.73</v>
+        <v>36.52</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>15</v>
@@ -9909,25 +10353,25 @@
         <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>322</v>
+        <v>467</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>24.57</v>
+        <v>36.04</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>15</v>
@@ -9938,28 +10382,28 @@
         <v>2020</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>24.51</v>
+        <v>35.71</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>15</v>
@@ -9970,28 +10414,28 @@
         <v>2020</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>24.49</v>
+        <v>34.8</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>15</v>
@@ -10002,28 +10446,28 @@
         <v>2020</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>24.3</v>
+        <v>34.72</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>15</v>
@@ -10037,25 +10481,25 @@
         <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>350</v>
+        <v>495</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>23.98</v>
+        <v>34.72</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>15</v>
@@ -10066,28 +10510,28 @@
         <v>2020</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>331</v>
+        <v>467</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>23.57</v>
+        <v>34.66</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>15</v>
@@ -10098,28 +10542,28 @@
         <v>2020</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>350</v>
+        <v>502</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>528</v>
+        <v>467</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>23.03</v>
+        <v>34.6</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>15</v>
@@ -10130,28 +10574,28 @@
         <v>2020</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>22.63</v>
+        <v>34.58</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>15</v>
@@ -10162,28 +10606,28 @@
         <v>2020</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>21.97</v>
+        <v>34.45</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>15</v>
@@ -10194,28 +10638,28 @@
         <v>2020</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>322</v>
+        <v>495</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>20.84</v>
+        <v>34.34</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>15</v>
@@ -10226,28 +10670,28 @@
         <v>2020</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>19.13</v>
+        <v>34.26</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>15</v>
@@ -10258,28 +10702,28 @@
         <v>2020</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>350</v>
+        <v>476</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>18.81</v>
+        <v>34.02</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>15</v>
@@ -10290,35 +10734,2307 @@
         <v>2020</v>
       </c>
       <c r="B258" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I258" s="2" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="J258" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B259" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G258" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I258" s="2" t="n">
+      <c r="C259" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H259" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I259" s="2" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="J259" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I260" s="2" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="J260" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H261" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I261" s="2" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="J261" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I262" s="2" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="J262" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H263" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I263" s="2" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="J263" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I264" s="2" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="J264" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H265" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I265" s="2" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="J265" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H266" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I266" s="2" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="J266" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H267" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I267" s="2" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="J267" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H268" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J268" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H269" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I269" s="2" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="J269" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H270" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I270" s="2" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="J270" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H271" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I271" s="2" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="J271" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H272" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I272" s="2" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="J272" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H273" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I273" s="2" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="J273" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F274" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H274" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I274" s="2" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="J274" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H275" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I275" s="2" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H276" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I276" s="2" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="J276" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H277" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I277" s="2" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="J277" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H278" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I278" s="2" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="J278" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H279" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I279" s="2" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="J279" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H280" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I280" s="2" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="J280" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H281" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I281" s="2" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J281" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H282" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I282" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J282" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F283" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H283" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I283" s="2" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="J283" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H284" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I284" s="2" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="J284" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G285" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H285" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I285" s="2" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="J285" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F286" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H286" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I286" s="2" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="J286" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H287" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I287" s="2" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="J287" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H288" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I288" s="2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J288" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H289" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I289" s="2" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="J289" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H290" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I290" s="2" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="J290" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F291" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H291" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I291" s="2" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="J291" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F292" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H292" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I292" s="2" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="J292" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H293" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I293" s="2" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="J293" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H294" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I294" s="2" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J294" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F295" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G295" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H295" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I295" s="2" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="J295" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F296" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H296" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I296" s="2" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="J296" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F297" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G297" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H297" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I297" s="2" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="J297" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F298" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H298" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I298" s="2" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="J298" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F299" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H299" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I299" s="2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J299" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F300" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G300" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H300" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I300" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J300" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F301" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G301" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H301" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I301" s="2" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="J301" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G302" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H302" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I302" s="2" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="J302" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F303" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G303" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H303" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I303" s="2" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="J303" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F304" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G304" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H304" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I304" s="2" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="J304" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F305" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G305" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H305" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I305" s="2" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="J305" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="F306" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G306" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H306" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I306" s="2" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="J306" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F307" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H307" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I307" s="2" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="J307" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F308" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G308" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H308" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I308" s="2" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="J308" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F309" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G309" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H309" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I309" s="2" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J309" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F310" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G310" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H310" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I310" s="2" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="J310" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F311" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G311" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H311" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I311" s="2" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="J311" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I312" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J312" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="F313" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G313" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H313" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I313" s="2" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="J313" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F314" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G314" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H314" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I314" s="2" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="J314" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F315" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G315" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H315" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I315" s="2" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="J315" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G316" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H316" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I316" s="2" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="J316" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F317" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G317" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H317" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I317" s="2" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="J317" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F318" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G318" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H318" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I318" s="2" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="J318" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F319" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G319" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H319" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I319" s="2" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="J319" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F320" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G320" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I320" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="J320" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F321" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G321" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H321" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I321" s="2" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="J321" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F322" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G322" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I322" s="2" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="J322" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F323" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G323" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H323" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I323" s="2" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="J323" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F324" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G324" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H324" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I324" s="2" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="J324" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B325" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F325" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H325" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I325" s="2" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="J325" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F326" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G326" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H326" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I326" s="2" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="J326" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F327" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H327" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I327" s="2" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="J327" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F328" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G328" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I328" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="J328" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F329" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G329" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I329" s="2" t="n">
         <v>16.45</v>
       </c>
-      <c r="J258" s="2" t="s">
+      <c r="J329" s="2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J258"/>
+  <autoFilter ref="A1:J329"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -10335,7 +13051,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>541</v>
+        <v>686</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -10343,50 +13059,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>542</v>
+        <v>687</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>543</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>544</v>
+        <v>689</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>545</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>546</v>
+        <v>691</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>547</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>548</v>
+        <v>693</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>547</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>549</v>
+        <v>695</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>547</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>550</v>
+        <v>697</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>547</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -10401,28 +13117,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>699</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>552</v>
+        <v>700</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>553</v>
+        <v>701</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>554</v>
+        <v>702</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -10431,7 +13147,7 @@
         <v>2020</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>555</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_o_ocup_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_o_ocup_a_2020.xlsx
@@ -2083,7 +2083,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:08</t>
+    <t xml:space="preserve">2026-09-08 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
